--- a/ykk-dsr/hub/tc-out/[Sutrix] DSR -585- [AEM] 製品CF 改修（項目fix版対応）_TestData.xlsx
+++ b/ykk-dsr/hub/tc-out/[Sutrix] DSR -585- [AEM] 製品CF 改修（項目fix版対応）_TestData.xlsx
@@ -518,12 +518,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1.0–3.0, 6.0, 7.0, 12.0–15.0</t>
+          <t>1.0–3.0, 6.0, 7.0, 12.0–16.0, 18.0</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Product CF full (all fields filled) + CF related</t>
+          <t>Product CF full (ver0.4, all fields filled) + CF related</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -533,12 +533,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>productId / productName / productCategories / applications / zipperChainTypeCategories / media01Asset / publishDate</t>
+          <t>productId / productCode / productName / productCategories / applications / zipperChainTypeCategories / openingType / media01Asset / media02Type+Url / description / itemVariations / colorVariations / howToUse / notice / printableTape / recycledMaterial / publishDate</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>990585001 / QA585 full product / any / any / CN / any QA image / 2026-10-01</t>
+          <t>990585001 / QA585-FULL / QA585 full product / any / any / 2 tags / 止+開 / any QA image / External + https://www.ykkfastening.com/ / 'QA585 description' / table 2×2 / 'QA585 colors' / 'QA585 how to use' / 'QA585 notice' / ON / ON / 2026-10-01</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4.0, 5.0</t>
+          <t>4.0, 5.0, 17.0</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>required fields only</t>
+          <t>7 required: productId, productCode, productName, productCategories, applications, media01Asset, publishDate</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>990585002 / QA585 required only / … / 2026-10-01</t>
+          <t>990585002 / QA585-REQ / QA585 required only / any / any / any QA image / 2026-10-01</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Wait until Dat/Claude confirms the fixed model is on DEV (Q27). Before that, run only 11.0 step 'record values' on TD-585-04 (read-only).</t>
+          <t>Wait until Dat/Claude confirms ver0.4 is finished on DEV (Martin ping). Before that, run only 11.0 step 'record values' on TD-585-04 (read-only).</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Model not updated → all others Not run (Blocked)</t>
+          <t>Not confirmed → all others Not run (Blocked)</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>TD-585-01: Assets → /content/dam/common/ja/products → Create → Content Fragment → model DM_product → name 990585001 → fill all fields (tags: pick any; media01Asset: any image under /content/dam/dsr/test) → Save → Publish. Then /content/dam/dsr/ja/products → Create CF model DM_product_dsr name 990585001, isActive ON, product = the CF above → Publish.</t>
+          <t>TD-585-01: https://author-p192812-e2014374.adobeaemcloud.com/assets.html/content/dam/common/ja/products → Create → Content Fragment → model DM_product → Name = 990585001 (same as productId, digits only, no prefix) → fill every field in the TestData row (7 required: productId, productCode, productName, productCategories, applications, media01Asset, publishDate) → Save → Publish. Then …/assets.html/content/dam/dsr/ja/products → Create CF model DM_product_dsr, Name 990585001, isActive ON, product = the CF above → Publish.</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Name must be digits only; no uppercase/_ (BL-OVL-1)</t>
+          <t>Name ≠ productId or not digits → page not generated (BL-OVL-1)</t>
         </is>
       </c>
     </row>
